--- a/Tests/Test Config From EXCEL/testdata/testconfigfromexceltablegetattributeasi32.xlsx
+++ b/Tests/Test Config From EXCEL/testdata/testconfigfromexceltablegetattributeasi32.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4034be38423d4008"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R25f795e2210b40dc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="s">
@@ -67,7 +67,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb3901a9e3c24d7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51152020b21e47aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Tests/Test Config From EXCEL/testdata/testconfigfromexceltablegetattributeasi32.xlsx
+++ b/Tests/Test Config From EXCEL/testdata/testconfigfromexceltablegetattributeasi32.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R25f795e2210b40dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6984cb44581a457f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -67,7 +67,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51152020b21e47aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc894828df8f4867"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Tests/Test Config From EXCEL/testdata/testconfigfromexceltablegetattributeasi32.xlsx
+++ b/Tests/Test Config From EXCEL/testdata/testconfigfromexceltablegetattributeasi32.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6984cb44581a457f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc296c43d0bb449f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="general" sheetId="2" r:id="R62718125afee4237"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -54,6 +55,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetData/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="s">
@@ -67,7 +74,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc894828df8f4867"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R551f2bd9be8148eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Tests/Test Config From EXCEL/testdata/testconfigfromexceltablegetattributeasi32.xlsx
+++ b/Tests/Test Config From EXCEL/testdata/testconfigfromexceltablegetattributeasi32.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc296c43d0bb449f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="general" sheetId="2" r:id="R62718125afee4237"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb25d78047b6d4bb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="general" sheetId="2" r:id="R315bfe1651304279"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -11,7 +11,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>Timing.SamplesPerChannel</x:t>
+    <x:t>Timing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{
+  "SamplesPerChannel": 1000
+}</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -47,7 +52,7 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="attributes" displayName="Attributes" ref="A1:A2" totalsRowShown="0">
   <x:tableColumns count="1">
-    <x:tableColumn id="1" name="Timing.SamplesPerChannel"/>
+    <x:tableColumn id="1" name="Timing"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -68,13 +73,13 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="n">
-        <x:v>1000</x:v>
+      <x:c r="A2" t="s">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R551f2bd9be8148eb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71cec88a5c754f4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>